--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128483840</v>
       </c>
       <c r="B2" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128484161</v>
       </c>
       <c r="B3" t="n">
-        <v>88528</v>
+        <v>88620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128483849</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128483937</v>
       </c>
       <c r="B5" t="n">
-        <v>90878</v>
+        <v>90970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128483826</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
+        <v>89502</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128484164</v>
       </c>
       <c r="B7" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128483840</v>
       </c>
       <c r="B2" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128484161</v>
       </c>
       <c r="B3" t="n">
-        <v>88620</v>
+        <v>88626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128483849</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128483937</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
+        <v>90976</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128483826</v>
       </c>
       <c r="B6" t="n">
-        <v>89502</v>
+        <v>89508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128484164</v>
       </c>
       <c r="B7" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128483840</v>
       </c>
       <c r="B2" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128484161</v>
       </c>
       <c r="B3" t="n">
-        <v>88626</v>
+        <v>88632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128483937</v>
       </c>
       <c r="B5" t="n">
-        <v>90976</v>
+        <v>90982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128483826</v>
       </c>
       <c r="B6" t="n">
-        <v>89508</v>
+        <v>89514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128483840</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128484161</v>
       </c>
       <c r="B3" t="n">
-        <v>88632</v>
+        <v>88634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128483849</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128483937</v>
       </c>
       <c r="B5" t="n">
-        <v>90982</v>
+        <v>90984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128483826</v>
       </c>
       <c r="B6" t="n">
-        <v>89514</v>
+        <v>89516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128484164</v>
       </c>
       <c r="B7" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128483840</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128483937</v>
       </c>
       <c r="B5" t="n">
-        <v>90984</v>
+        <v>90985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128483840</v>
       </c>
       <c r="B2" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128484161</v>
       </c>
       <c r="B3" t="n">
-        <v>88634</v>
+        <v>88661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128483849</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128483937</v>
       </c>
       <c r="B5" t="n">
-        <v>90985</v>
+        <v>91012</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128483826</v>
       </c>
       <c r="B6" t="n">
-        <v>89516</v>
+        <v>89543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128484164</v>
       </c>
       <c r="B7" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128483840</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128484161</v>
       </c>
       <c r="B3" t="n">
-        <v>88661</v>
+        <v>88665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128483849</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128483937</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91017</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128483826</v>
       </c>
       <c r="B6" t="n">
-        <v>89543</v>
+        <v>89548</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128484164</v>
       </c>
       <c r="B7" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128483840</v>
       </c>
       <c r="B2" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128484161</v>
       </c>
       <c r="B3" t="n">
-        <v>88665</v>
+        <v>88666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128483937</v>
       </c>
       <c r="B5" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128483826</v>
       </c>
       <c r="B6" t="n">
-        <v>89548</v>
+        <v>89553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128483840</v>
       </c>
       <c r="B2" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128484161</v>
       </c>
       <c r="B3" t="n">
-        <v>88666</v>
+        <v>88670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128483849</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128483937</v>
       </c>
       <c r="B5" t="n">
-        <v>91022</v>
+        <v>91026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128483826</v>
       </c>
       <c r="B6" t="n">
-        <v>89553</v>
+        <v>89557</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128484164</v>
       </c>
       <c r="B7" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128483840</v>
       </c>
       <c r="B2" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128484161</v>
       </c>
       <c r="B3" t="n">
-        <v>88670</v>
+        <v>88675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128483849</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128483937</v>
       </c>
       <c r="B5" t="n">
-        <v>91026</v>
+        <v>91031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>128483826</v>
       </c>
       <c r="B6" t="n">
-        <v>89557</v>
+        <v>89562</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>128484164</v>
       </c>
       <c r="B7" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128483937</v>
       </c>
       <c r="B7" t="n">
-        <v>91038</v>
+        <v>91041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128483937</v>
       </c>
       <c r="B7" t="n">
-        <v>91041</v>
+        <v>91044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128483937</v>
       </c>
       <c r="B7" t="n">
-        <v>91044</v>
+        <v>91048</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128483937</v>
       </c>
       <c r="B7" t="n">
-        <v>91048</v>
+        <v>91055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128483937</v>
       </c>
       <c r="B7" t="n">
-        <v>91055</v>
+        <v>91057</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128483937</v>
       </c>
       <c r="B7" t="n">
-        <v>91057</v>
+        <v>91058</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128483937</v>
       </c>
       <c r="B7" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128483937</v>
       </c>
       <c r="B7" t="n">
-        <v>91061</v>
+        <v>91063</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128483937</v>
       </c>
       <c r="B7" t="n">
-        <v>91063</v>
+        <v>91067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128483937</v>
       </c>
       <c r="B7" t="n">
-        <v>91067</v>
+        <v>91068</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -1188,7 +1188,7 @@
         <v>128483937</v>
       </c>
       <c r="B7" t="n">
-        <v>91068</v>
+        <v>91071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128483840</v>
+        <v>128483826</v>
       </c>
       <c r="B2" t="n">
-        <v>92451</v>
+        <v>89941</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>275</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kejsarskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Catathelasma imperiale</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128484161</v>
+        <v>128484164</v>
       </c>
       <c r="B3" t="n">
-        <v>88677</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>239221</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Papegojvaxing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Herink</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405809</v>
+        <v>405813</v>
       </c>
       <c r="R3" t="n">
-        <v>7024569</v>
+        <v>7024566</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128483849</v>
+        <v>128483840</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128483826</v>
+        <v>128483849</v>
       </c>
       <c r="B5" t="n">
-        <v>89564</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>275</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kejsarskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Catathelasma imperiale</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,34 +1083,25 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128484164</v>
+        <v>128484161</v>
       </c>
       <c r="B6" t="n">
-        <v>80135</v>
+        <v>89060</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>239221</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Gliophorus psittacinus var. psittacinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1118,10 +1109,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405813</v>
+        <v>405809</v>
       </c>
       <c r="R6" t="n">
-        <v>7024566</v>
+        <v>7024569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128483937</v>
+        <v>128484141</v>
       </c>
       <c r="B7" t="n">
-        <v>91071</v>
+        <v>90668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5749</v>
+        <v>245031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Citronfingersvamp</t>
+          <t>Borgsjömusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria gypsea</t>
+          <t>Tricholoma borgsjoeënse</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schild</t>
+          <t>Jacobsson &amp; Muskos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,14 +1210,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sönnestbäcken, Sönnestbäcken, Jmt</t>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405975</v>
+        <v>405799</v>
       </c>
       <c r="R7" t="n">
-        <v>7024664</v>
+        <v>7024595</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,11 +1258,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128483826</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484164</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128483840</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128483849</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484161</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,8 +1309,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484141</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128483840</v>
+        <v>128484161</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>89206</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>4393</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Papegojvaxing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Gliophorus psittacinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Schaeff.) Herink</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sönnestbäcken, Sönnestbäcken, Jmt</t>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405978</v>
+        <v>405809</v>
       </c>
       <c r="R4" t="n">
-        <v>7024662</v>
+        <v>7024569</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,38 +995,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128483840</t>
+          <t>https://artportalen.se/Sighting/128484161</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128483849</v>
+        <v>128483840</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1102,42 +1102,51 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128483849</t>
+          <t>https://artportalen.se/Sighting/128483840</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128484161</v>
+        <v>128483849</v>
       </c>
       <c r="B6" t="n">
-        <v>89060</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>239221</v>
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus var. psittacinus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+          <t>Sönnestbäcken, Sönnestbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405809</v>
+        <v>405978</v>
       </c>
       <c r="R6" t="n">
-        <v>7024569</v>
+        <v>7024662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1209,7 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128484161</t>
+          <t>https://artportalen.se/Sighting/128483849</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128484161</v>
       </c>
       <c r="B4" t="n">
-        <v>89206</v>
+        <v>89207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128484161</v>
       </c>
       <c r="B4" t="n">
-        <v>89207</v>
+        <v>89213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128484161</v>
       </c>
       <c r="B4" t="n">
-        <v>89213</v>
+        <v>89220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128484161</v>
       </c>
       <c r="B4" t="n">
-        <v>89220</v>
+        <v>89221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128484161</v>
       </c>
       <c r="B4" t="n">
-        <v>89221</v>
+        <v>89234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4938-2025 artfynd.xlsx
+++ b/artfynd/A 4938-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128484161</v>
       </c>
       <c r="B4" t="n">
-        <v>89234</v>
+        <v>89235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
